--- a/astro-site/public/dl/chocolate-shop-checklist-templates/08-chocolate-store-opening-closing-checklist.xlsx
+++ b/astro-site/public/dl/chocolate-shop-checklist-templates/08-chocolate-store-opening-closing-checklist.xlsx
@@ -1731,13 +1731,13 @@
       <c r="G8" s="19" t="inlineStr"/>
       <c r="H8" s="20" t="inlineStr"/>
     </row>
-    <row r="9" ht="33.25" customHeight="1">
+    <row r="9" ht="47" customHeight="1">
       <c r="A9" s="17" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="18" t="inlineStr">
         <is>
-          <t>Turn off the chocolate display cases once all the product is back in the cool room</t>
+          <t>Turn off the chocolate display cases once all the product is back in the cool room (TCS fresh-cream items: fridge)</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
@@ -1843,13 +1843,13 @@
       <c r="G12" s="19" t="inlineStr"/>
       <c r="H12" s="20" t="inlineStr"/>
     </row>
-    <row r="13" ht="47" customHeight="1">
+    <row r="13" ht="60.5" customHeight="1">
       <c r="A13" s="17" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="18" t="inlineStr">
         <is>
-          <t>Final safety check: gas appliances off (if you have gas), water off, small appliances unplugged — never the cool room or the fridges</t>
+          <t>Final safety check: gas appliances off (if you have gas), no taps left running, small appliances unplugged — never the cool room, the fridges or a melter kept on overnight</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
@@ -1899,13 +1899,13 @@
       <c r="G14" s="19" t="inlineStr"/>
       <c r="H14" s="20" t="inlineStr"/>
     </row>
-    <row r="15" ht="33.25" customHeight="1">
+    <row r="15" ht="47" customHeight="1">
       <c r="A15" s="17" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="18" t="inlineStr">
         <is>
-          <t>Turn off HVAC or set it to night mode: keep the shop below 68 °F if any chocolate stays out of the cool room</t>
+          <t>Set HVAC to night mode — never fully off in warm weather: wrapped bars on the shelves need the shop at 68 °F or below overnight</t>
         </is>
       </c>
       <c r="C15" s="19" t="inlineStr">
